--- a/cleaning_pipeline_R/neotree_scripts/zim-scripts/Parirenyatwa Group of Hospitals Discharge - metadata.xlsx
+++ b/cleaning_pipeline_R/neotree_scripts/zim-scripts/Parirenyatwa Group of Hospitals Discharge - metadata.xlsx
@@ -485,10 +485,10 @@
         <v>form</v>
       </c>
       <c r="F2" t="str">
-        <v>NeoTreeOutcome</v>
+        <v>NeotreeOutcome</v>
       </c>
       <c r="G2" t="str">
-        <v>Outcome</v>
+        <v>Outcome at discharge</v>
       </c>
       <c r="H2" t="str">
         <v>dropdown</v>
@@ -509,7 +509,7 @@
         <v/>
       </c>
       <c r="N2" t="str">
-        <v>[{"value":"DC","valueLabel":"Discharged"},{"value":"NND","valueLabel":"Died"},{"value":"DDA","valueLabel":"Died During Admission"},{"value":"ABS","valueLabel":"Absconded"},{"value":"TRH","valueLabel":"Transferred to other Hospital"},{"value":"TRO","valueLabel":"Transferred to another ward (example: paediatric ward)"},{"value":"DAMA","valueLabel":"Discharged against medical advice"},{"value":"BID","valueLabel":"Brought in dead"}]</v>
+        <v>[{"value":"DC","valueLabel":"Discharged"},{"value":"NND","valueLabel":"Died"},{"value":"DDA","valueLabel":"Died during admission"},{"value":"ABS","valueLabel":"Absconded"},{"value":"TRH","valueLabel":"Transferred to other hospital"},{"value":"TRO","valueLabel":"Transferred to another ward (example: paediatric ward)"},{"value":"DAMA","valueLabel":"Discharged against medical advice"},{"value":"BID","valueLabel":"Brought in dead"}]</v>
       </c>
       <c r="O2" t="str">
         <v/>
@@ -2052,7 +2052,7 @@
         <v>AdmReason</v>
       </c>
       <c r="G25" t="str">
-        <v>Presenting Complaint</v>
+        <v>Presenting complaint</v>
       </c>
       <c r="H25" t="str">
         <v>dropdown</v>
@@ -2073,7 +2073,7 @@
         <v/>
       </c>
       <c r="N25" t="str">
-        <v>[{"value":"An","valueLabel":"Anaemia"},{"value":"BBA","valueLabel":"Born before arrival"},{"value":"BI","valueLabel":"Birth Trauma"},{"value":"Cong","valueLabel":"Congenital Abnormality"},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease"},{"value":"Conv","valueLabel":"Convulsions"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"DF","valueLabel":"Difficulty feeding"},{"value":"DUM","valueLabel":"Abandoned baby"},{"value":"Fev","valueLabel":"Fever"},{"value":"HIVLR","valueLabel":"HIV low risk"},{"value":"HIVHR","valueLabel":"HIV high risk"},{"value":"HIVU","valueLabel":"HIV unknown"},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)"},{"value":"HypogSy","valueLabel":"Hypoglycaemia (Symptomatic)"},{"value":"RiHypog","valueLabel":"Risk of hypoglycaemia"},{"value":"BA","valueLabel":"Hypoxic Ischaemic Encephalopathy"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"MJ","valueLabel":"Physiological Jaundice"},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)"},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)"},{"value":"ExLBW","valueLabel":"ExtremelyLow Birth Weight (&lt;1000g)"},{"value":"MA","valueLabel":"Possible Meconium Aspiration"},{"value":"MecEx","valueLabel":"Meconium exposure (asymptomatic baby)"},{"value":"MiHypo","valueLabel":"Mild Hypothermia"},{"value":"ModHypo","valueLabel":"Moderate Hypothermia"},{"value":"SHypo","valueLabel":"Severe Hypothermia"},{"value":"Hyperth","valueLabel":"Hyperthermia"},{"value":"NB","valueLabel":"Normal baby"},{"value":"PN","valueLabel":"Pneumonia"},{"value":"Prem","valueLabel":"Premature (32-36 weeks)"},{"value":"VPrem","valueLabel":"Very Premature (28-31 weeks)"},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)"},{"value":"PremRD","valueLabel":"Prematurity with Respiratory distress"},{"value":"Risk","valueLabel":"Risk factors for sepsis"},{"value":"NSep","valueLabel":"Suspected neonatal sepsis"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)"},{"value":"OTH","valueLabel":"Other"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"TermRD","valueLabel":"Term with Respiratory distress"},{"value":"DJ","valueLabel":"Pathological Jaundice"},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy"},{"value":"PJaundice","valueLabel":"Prolonged Jaundice"},{"value":"CleftLip","valueLabel":"Cleft lip"},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD"},{"value":"CleftLipPalate","valueLabel":"Cleft lip and/or palate"},{"value":"Omph","valueLabel":"Omphalocele"},{"value":"Myelo","valueLabel":"Myelomeningocele"},{"value":"CDH","valueLabel":"Congenital Dislocation of the hip (CDH)"},{"value":"MiTalipes","valueLabel":"Mild Talipes (club foot)"},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)"}]</v>
+        <v>[{"value":"An","valueLabel":"Anaemia"},{"value":"BBA","valueLabel":"Born before arrival"},{"value":"BI","valueLabel":"Birth Trauma"},{"value":"Cong","valueLabel":"Congenital Abnormality"},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease"},{"value":"Conv","valueLabel":"Convulsions"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"DF","valueLabel":"Difficulty feeding"},{"value":"DUM","valueLabel":"Abandoned baby"},{"value":"Fev","valueLabel":"Fever"},{"value":"HIVLR","valueLabel":"HIV low risk"},{"value":"HIVHR","valueLabel":"HIV high risk"},{"value":"HIVU","valueLabel":"HIV unknown"},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)"},{"value":"HypogSy","valueLabel":"Hypoglycaemia (symptomatic)"},{"value":"RiHypog","valueLabel":"Risk of hypoglycaemia"},{"value":"HIE","valueLabel":"Birth Asphyxia / Hypoxic Ischaemic Encephalopathy (HIE)"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"MJ","valueLabel":"Jaundice (physiological)"},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)"},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)"},{"value":"ExLBW","valueLabel":"ExtremelyLow Birth Weight (&lt;1000g)"},{"value":"MA","valueLabel":"Possible Meconium Aspiration"},{"value":"MecEx","valueLabel":"Meconium exposure (asymptomatic baby)"},{"value":"MiHypo","valueLabel":"Mild Hypothermia"},{"value":"ModHypo","valueLabel":"Moderate Hypothermia"},{"value":"SHypo","valueLabel":"Severe Hypothermia"},{"value":"Hyperth","valueLabel":"Hyperthermia"},{"value":"NB","valueLabel":"Normal baby"},{"value":"PN","valueLabel":"Pneumonia"},{"value":"Prem","valueLabel":"Premature (32-36 weeks)"},{"value":"VPrem","valueLabel":"Very Premature (28 to 31.6 weeks)"},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)"},{"value":"PremRD","valueLabel":"Prematurity with Respiratory distress"},{"value":"Risk","valueLabel":"Risk factors for sepsis"},{"value":"NSep","valueLabel":"Sepsis suspected"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)"},{"value":"OTH","valueLabel":"Other"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"TermRD","valueLabel":"Term with Respiratory distress"},{"value":"DJ","valueLabel":"Jaundice (pathological)"},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy"},{"value":"ProJ","valueLabel":"Jaundice (prolonged)"},{"value":"CleftLip","valueLabel":"Cleft lip"},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD"},{"value":"CleftLipPalate","valueLabel":"Cleft lip and/or palate"},{"value":"Omph","valueLabel":"Omphalocele"},{"value":"Myelo","valueLabel":"Myelomeningocele"},{"value":"CDH","valueLabel":"Congenital dislocation of the hip (CDH)"},{"value":"MiTalipes","valueLabel":"Talipes MILD (club foot)"},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)"}]</v>
       </c>
       <c r="O25" t="str">
         <v>$NeoTreeOutcome != 'BID'</v>
@@ -2679,13 +2679,13 @@
         <v>No</v>
       </c>
       <c r="L34" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M34" t="str">
         <v/>
       </c>
       <c r="N34" t="str">
-        <v>[{"value":"PGH","valueLabel":"Parirenyatwa Group of Hospitals"},{"value":"OtH","valueLabel":"Other clinic in Harare"},{"value":"OtR","valueLabel":"Other clinic outside Harare"},{"value":"H","valueLabel":"Home"}]</v>
+        <v>[{"value":"PGH","valueLabel":"Parirenyatwa Group of Hospitals"},{"value":"OthHarare","valueLabel":"Other clinic in Harare"},{"value":"OtR","valueLabel":"Other clinic outside Harare"},{"value":"H","valueLabel":"Home"}]</v>
       </c>
       <c r="O34" t="str">
         <v>$NeoTreeOutcome != 'BID'</v>
@@ -2732,7 +2732,7 @@
         <v>Gestation</v>
       </c>
       <c r="G35" t="str">
-        <v>Gestation at birth (weeks.days)</v>
+        <v>Estimated Gestational age at birth (weeks.days)</v>
       </c>
       <c r="H35" t="str">
         <v>number</v>
@@ -3433,7 +3433,7 @@
         <v/>
       </c>
       <c r="N45" t="str">
-        <v>[{"value":"An","valueLabel":"Anaemia"},{"value":"BBA","valueLabel":"Born before arrival"},{"value":"BI","valueLabel":"Birth Trauma"},{"value":"Cong","valueLabel":"Congenital Abnormality"},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease"},{"value":"Conv","valueLabel":"Convulsions"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"DF","valueLabel":"Difficulty feeding"},{"value":"DUM","valueLabel":"Abandoned baby"},{"value":"HIVExp","valueLabel":"HIV Exposed"},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)"},{"value":"HypogSy","valueLabel":"Hypoglycaemia (Symptomatic)"},{"value":"RiHypog","valueLabel":"Risk of hypoglycaemia"},{"value":"BA","valueLabel":"Hypoxic Ischaemic Encephalopathy"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"MJ","valueLabel":"Physiological Jaundice"},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)"},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)"},{"value":"ExLBW","valueLabel":"Extremely Low Birth Weight (&lt;1000g)"},{"value":"MA","valueLabel":"Possible Meconium Aspiration"},{"value":"MecEx","valueLabel":"Meconium exposure (asymptomatic baby)"},{"value":"MiHypo","valueLabel":"Mild Hypothermia"},{"value":"ModHypo","valueLabel":"Moderate Hypothermia"},{"value":"SHypo","valueLabel":"Severe Hypothermia"},{"value":"Hyperth","valueLabel":"Hyperthermia"},{"value":"NB","valueLabel":"Normal baby"},{"value":"PN","valueLabel":"Pneumonia"},{"value":"Prem","valueLabel":"Premature (32-36 weeks)"},{"value":"VPrem","valueLabel":"Very Premature (28-31 weeks)"},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)"},{"value":"PremRD","valueLabel":"Prematurity with Respiratory distress"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"TermRD","valueLabel":"Term with Respiratory distress"},{"value":"DJPh","valueLabel":"Pathological jaundice (phototherapy range)"},{"value":"DJEx","valueLabel":"Pathological jaundice (Exchange transfusion required)"},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy"},{"value":"PJaundice","valueLabel":"Prolonged Jaundice"},{"value":"CleftLip","valueLabel":"Cleft lip"},{"value":"EONS","valueLabel":"Neonatal Sepsis - Early Onset (EONS)"},{"value":"LONS","valueLabel":"Neonatal Sepsis - Late Onset (LONS)"},{"value":"NSepNC","valueLabel":"Risk factors for sepsis (but sepsis ruled out)"},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD"},{"value":"CleftLipPalate","valueLabel":"Cleft lip and/or palate"},{"value":"Omph","valueLabel":"Omphalocele"},{"value":"Myelo","valueLabel":"Myelomeningocele"},{"value":"CDH","valueLabel":"Congenital Dislocation of the hip (CDH)"},{"value":"MiTalipes","valueLabel":"Mild Talipes (club foot)"},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)"},{"value":"OTH","valueLabel":"Other"}]</v>
+        <v>[{"value":"An","valueLabel":"Anaemia"},{"value":"BBA","valueLabel":"Born before arrival"},{"value":"BI","valueLabel":"Birth Trauma"},{"value":"Cong","valueLabel":"Congenital Abnormality"},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease"},{"value":"Conv","valueLabel":"Convulsions"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"DF","valueLabel":"Difficulty feeding"},{"value":"DUM","valueLabel":"Abandoned baby"},{"value":"HIVExp","valueLabel":"HIV Exposed"},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)"},{"value":"HypogSy","valueLabel":"Hypoglycaemia (symptomatic)"},{"value":"RiHypog","valueLabel":"Risk of hypoglycaemia"},{"value":"HIE","valueLabel":"Birth Asphyxia / Hypoxic Ischaemic Encephalopathy (HIE)"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"MJ","valueLabel":"Jaundice (physiological)"},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)"},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)"},{"value":"ExLBW","valueLabel":"Extremely Low Birth Weight (&lt;1000g)"},{"value":"MA","valueLabel":"Possible Meconium Aspiration"},{"value":"MecEx","valueLabel":"Meconium exposure (asymptomatic baby)"},{"value":"MiHypo","valueLabel":"Mild Hypothermia"},{"value":"ModHypo","valueLabel":"Moderate Hypothermia"},{"value":"SHypo","valueLabel":"Severe Hypothermia"},{"value":"Hyperth","valueLabel":"Hyperthermia"},{"value":"NB","valueLabel":"Normal baby"},{"value":"PN","valueLabel":"Pneumonia"},{"value":"Prem","valueLabel":"Premature (32-36 weeks)"},{"value":"VPrem","valueLabel":"Very Premature (28 to 31.6 weeks)"},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)"},{"value":"PremRD","valueLabel":"Prematurity with Respiratory distress"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"TermRD","valueLabel":"Term with Respiratory distress"},{"value":"DJPh","valueLabel":"Pathological jaundice (phototherapy range)"},{"value":"DJEx","valueLabel":"Pathological jaundice (Exchange transfusion required)"},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy"},{"value":"ProJ","valueLabel":"Jaundice (prolonged)"},{"value":"CleftLip","valueLabel":"Cleft lip"},{"value":"EONS","valueLabel":"Neonatal Sepsis - Early Onset (EONS)"},{"value":"LONS","valueLabel":"Neonatal Sepsis - Late Onset (LONS)"},{"value":"NSepNC","valueLabel":"Sepsis (risk factors, but ruled out)"},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD"},{"value":"CleftLipPalate","valueLabel":"Cleft lip and/or palate"},{"value":"Omph","valueLabel":"Omphalocele"},{"value":"Myelo","valueLabel":"Myelomeningocele"},{"value":"CDH","valueLabel":"Congenital dislocation of the hip (CDH)"},{"value":"MiTalipes","valueLabel":"Talipes MILD (club foot)"},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)"},{"value":"OTH","valueLabel":"Other"}]</v>
       </c>
       <c r="O45" t="str">
         <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome =  'ABS' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO'</v>
@@ -3977,7 +3977,7 @@
         <v/>
       </c>
       <c r="N53" t="str">
-        <v>[{"value":"An","valueLabel":"Anaemia"},{"value":"BBA","valueLabel":"Born before arrival"},{"value":"BI","valueLabel":"Birth Trauma"},{"value":"Cong","valueLabel":"Congenital Abnormality"},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease"},{"value":"Conv","valueLabel":"Convulsions"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"DF","valueLabel":"Difficulty feeding"},{"value":"DUM","valueLabel":"Abandoned baby"},{"value":"HIV","valueLabel":"HIV exposed"},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)"},{"value":"HypogSy","valueLabel":"Hypoglycaemia (Symptomatic)"},{"value":"RiHypog","valueLabel":"Risk of hypoglycaemia"},{"value":"BA","valueLabel":"Hypoxic Ischaemic Encephalopathy"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"MJ","valueLabel":"Physiological Jaundice"},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)"},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)"},{"value":"ExLBW","valueLabel":"ExtremelyLow Birth Weight (&lt;1000g)"},{"value":"MA","valueLabel":"Possible Meconium Aspiration"},{"value":"MecEx","valueLabel":"Meconium exposure (asymptomatic baby)"},{"value":"MiHypo","valueLabel":"Mild Hypothermia"},{"value":"ModHypo","valueLabel":"Moderate Hypothermia"},{"value":"SHypo","valueLabel":"Severe Hypothermia"},{"value":"Hyperth","valueLabel":"Hyperthermia"},{"value":"NB","valueLabel":"Normal baby"},{"value":"PN","valueLabel":"Pneumonia"},{"value":"Prem","valueLabel":"Premature (32-36 weeks)"},{"value":"VPrem","valueLabel":"Very Premature (28-31 weeks)"},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)"},{"value":"PremRD","valueLabel":"Prematurity with Respiratory distress"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"TermRD","valueLabel":"Term with Respiratory distress"},{"value":"DJPh","valueLabel":"Pathological jaundice (phototherapy range)"},{"value":"DJEx","valueLabel":"Pathological jaundice (exchange transfusion required)"},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy"},{"value":"PJaundice","valueLabel":"Prolonged Jaundice"},{"value":"CleftLip","valueLabel":"Cleft lip"},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD"},{"value":"CleftLipPalate","valueLabel":"Cleft lip and/or palate"},{"value":"EONS","valueLabel":"Neonatal Sepsis - Early Onset (EONS)"},{"value":"LONS","valueLabel":"Neonatal Sepsis - Late Onset (LONS)"},{"value":"Omph","valueLabel":"Omphalocele"},{"value":"Myelo","valueLabel":"Myelomeningocele"},{"value":"CDH","valueLabel":"Congenital Dislocation of the hip (CDH)"},{"value":"MiTalipes","valueLabel":"Mild Talipes (club foot)"},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)"},{"value":"OTH","valueLabel":"Other"}]</v>
+        <v>[{"value":"An","valueLabel":"Anaemia"},{"value":"BBA","valueLabel":"Born before arrival"},{"value":"BI","valueLabel":"Birth Trauma"},{"value":"Cong","valueLabel":"Congenital Abnormality"},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease"},{"value":"Conv","valueLabel":"Convulsions"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"DF","valueLabel":"Difficulty feeding"},{"value":"DUM","valueLabel":"Abandoned baby"},{"value":"HIV","valueLabel":"HIV exposed"},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)"},{"value":"HypogSy","valueLabel":"Hypoglycaemia (symptomatic)"},{"value":"RiHypog","valueLabel":"Risk of hypoglycaemia"},{"value":"HIE","valueLabel":"Birth Asphyxia / Hypoxic Ischaemic Encephalopathy (HIE)"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"MJ","valueLabel":"Jaundice (physiological)"},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)"},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)"},{"value":"ExLBW","valueLabel":"ExtremelyLow Birth Weight (&lt;1000g)"},{"value":"MA","valueLabel":"Possible Meconium Aspiration"},{"value":"MecEx","valueLabel":"Meconium exposure (asymptomatic baby)"},{"value":"MiHypo","valueLabel":"Mild Hypothermia"},{"value":"ModHypo","valueLabel":"Moderate Hypothermia"},{"value":"SHypo","valueLabel":"Severe Hypothermia"},{"value":"Hyperth","valueLabel":"Hyperthermia"},{"value":"NB","valueLabel":"Normal baby"},{"value":"PN","valueLabel":"Pneumonia"},{"value":"Prem","valueLabel":"Premature (32-36 weeks)"},{"value":"VPrem","valueLabel":"Very Premature (28 to 31.6 weeks)"},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)"},{"value":"PremRD","valueLabel":"Prematurity with Respiratory distress"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"TermRD","valueLabel":"Term with Respiratory distress"},{"value":"DJPh","valueLabel":"Pathological jaundice (phototherapy range)"},{"value":"DJEx","valueLabel":"Pathological jaundice (exchange transfusion required)"},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy"},{"value":"ProJ","valueLabel":"Jaundice (prolonged)"},{"value":"CleftLip","valueLabel":"Cleft lip"},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD"},{"value":"CleftLipPalate","valueLabel":"Cleft lip and/or palate"},{"value":"EONS","valueLabel":"Neonatal Sepsis - Early Onset (EONS)"},{"value":"LONS","valueLabel":"Neonatal Sepsis - Late Onset (LONS)"},{"value":"Omph","valueLabel":"Omphalocele"},{"value":"Myelo","valueLabel":"Myelomeningocele"},{"value":"CDH","valueLabel":"Congenital dislocation of the hip (CDH)"},{"value":"MiTalipes","valueLabel":"Talipes MILD (club foot)"},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)"},{"value":"OTH","valueLabel":"Other"}]</v>
       </c>
       <c r="O53" t="str">
         <v>$NeoTreeOutcome = 'NND' or $NeoTreeOutcome = 'DDA'</v>
@@ -4793,7 +4793,7 @@
         <v>$BC = true</v>
       </c>
       <c r="N65" t="str">
-        <v>[{"value":"NO","valueLabel":"No Growth"},{"value":"CO","valueLabel":"Likely Contaminant Organism"},{"value":"BS","valueLabel":"Bacillus Sp"},{"value":"CONS","valueLabel":"Coagulase Negative Staphylococcus"},{"value":"EC","valueLabel":"E.Coli"},{"value":"GBS","valueLabel":"Group B Streptococcus"},{"value":"GDS","valueLabel":"Group D Streptococcus"},{"value":"KP","valueLabel":"Klebsiella Pneumoniae"},{"value":"PA","valueLabel":"Pseudomonas Aeruginosa"},{"value":"SA","valueLabel":"Staphylococcus Aureus"},{"value":"LFC","valueLabel":"Lactose Fermenting Coliform"},{"value":"NLFC","valueLabel":"Non Lactose Fermenting Coliform"},{"value":"OGN","valueLabel":"Other Gram Negative"},{"value":"OGP","valueLabel":"Other Gram Positive"},{"value":"OTH","valueLabel":"Other"}]</v>
+        <v>[{"value":"NO","valueLabel":"No Growth"},{"value":"CO","valueLabel":"Likely Contaminant Organism"},{"value":"BS","valueLabel":"Bacillus Sp"},{"value":"CONS","valueLabel":"Coagulase Negative Staphylococcus"},{"value":"EC","valueLabel":"E.Coli"},{"value":"GBS","valueLabel":"Group B Streptococcus"},{"value":"GDS","valueLabel":"Group D Streptococcus"},{"value":"SA","valueLabel":"Staphylococcus Aureus"},{"value":"LFC","valueLabel":"Lactose Fermenting Coliform"},{"value":"NLFC","valueLabel":"Non Lactose Fermenting Coliform"},{"value":"OGN","valueLabel":"Other Gram Negative"},{"value":"OGP","valueLabel":"Other Gram Positive"},{"value":"OTH","valueLabel":"Other"}]</v>
       </c>
       <c r="O65" t="str">
         <v>$FBC = true or $CRP = true or $BC = true or $UE = true or $Bili = true or $TORCH = true or $Bone = true or $GLUC = true or $HIVPCRInf = true or $MatRPR = true or $MatHIVP = true</v>
@@ -7513,7 +7513,7 @@
         <v>$BC2 = true</v>
       </c>
       <c r="N105" t="str">
-        <v>[{"value":"NO","valueLabel":"No Organisms"},{"value":"CO","valueLabel":"Likely Contaminant Organism"},{"value":"BS","valueLabel":"Bacillus sp."},{"value":"CONS","valueLabel":"Coagulase negative staphylococcus"},{"value":"EC","valueLabel":"E.Coli"},{"value":"GBS","valueLabel":"Group B Streptococcus"},{"value":"KP","valueLabel":"Klabsiella Pneumoniae"},{"value":"PA","valueLabel":"Pseudomonas Aeruginosa"},{"value":"SA","valueLabel":"Staphylococcus Aureus"},{"value":"LFC","valueLabel":"Lactose Fermenting Coliform"},{"value":"NLFC","valueLabel":"Non Lactose Fermenting Coliform"},{"value":"OGN","valueLabel":"Other Gram Negative"},{"value":"OGP","valueLabel":"Other Gram Positive"},{"value":"OTH","valueLabel":"Other"},{"value":"","valueLabel":""}]</v>
+        <v>[{"value":"NO","valueLabel":"No Organisms"},{"value":"CO","valueLabel":"Likely Contaminant Organism"},{"value":"BS","valueLabel":"Bacillus sp."},{"value":"CONS","valueLabel":"Coagulase negative staphylococcus"},{"value":"EC","valueLabel":"E.Coli"},{"value":"GBS","valueLabel":"Group B Streptococcus"},{"value":"KP","valueLabel":"Klabsiella Pneumoniae"},{"value":"SA","valueLabel":"Staphylococcus Aureus"},{"value":"LFC","valueLabel":"Lactose Fermenting Coliform"},{"value":"NLFC","valueLabel":"Non Lactose Fermenting Coliform"},{"value":"OGN","valueLabel":"Other Gram Negative"},{"value":"OGP","valueLabel":"Other Gram Positive"},{"value":"OTH","valueLabel":"Other"},{"value":"","valueLabel":""}]</v>
       </c>
       <c r="O105" t="str">
         <v>$FBC2 = true or $CRP2 = true or $BC2 = true or $UE2 = true or $Bili2 = true or $Bone2 = true or $GLUC2 = true</v>
@@ -9145,7 +9145,7 @@
         <v>$LP = 'YesP'</v>
       </c>
       <c r="N129" t="str">
-        <v>[{"value":"CO","valueLabel":"Likely contaminant organism"},{"value":"BS","valueLabel":"Bacillus sp"},{"value":"CONS","valueLabel":"Coagulase negative staphylococcus"},{"value":"EC","valueLabel":"E. coli"},{"value":"GBS","valueLabel":"Group B Streptococcus"},{"value":"GDS","valueLabel":"Group D Streptococcus"},{"value":"KP","valueLabel":"Klebsiella pneumoniae"},{"value":"PA","valueLabel":"Pseudomonas aeruginosa"},{"value":"SA","valueLabel":"Staphylococcus aureus"},{"value":"LFC","valueLabel":"Lactose Fermenting Coliform"},{"value":"NLFC","valueLabel":"Non Lactose fermenting coliform"},{"value":"TB","valueLabel":"Mycobacterium tuberculosis"},{"value":"OGN","valueLabel":"Other Gram negative"},{"value":"OGP","valueLabel":"Other Gram positive"}]</v>
+        <v>[{"value":"CO","valueLabel":"Likely contaminant organism"},{"value":"BS","valueLabel":"Bacillus sp"},{"value":"CONS","valueLabel":"Coagulase negative staphylococcus"},{"value":"EC","valueLabel":"E. coli"},{"value":"GBS","valueLabel":"Group B Streptococcus"},{"value":"GDS","valueLabel":"Group D Streptococcus"},{"value":"SA","valueLabel":"Staphylococcus aureus"},{"value":"LFC","valueLabel":"Lactose Fermenting Coliform"},{"value":"NLFC","valueLabel":"Non Lactose fermenting coliform"},{"value":"TB","valueLabel":"Mycobacterium tuberculosis"},{"value":"OGN","valueLabel":"Other Gram negative"},{"value":"OGP","valueLabel":"Other Gram positive"}]</v>
       </c>
       <c r="O129" t="str">
         <v>$LP = 'YesN' or $LP = 'YesP'</v>
@@ -13683,7 +13683,7 @@
         <v>$SPECREV = 'Y'</v>
       </c>
       <c r="N195" t="str">
-        <v>[{"value":"Neph","valueLabel":"Nephrology","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ortho","valueLabel":"Orthopaedic Surgery","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Surg","valueLabel":"Surgical","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Opth","valueLabel":"Opthalmology","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MxFx","valueLabel":"Maxillofacial Surgery","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Neuro","valueLabel":"Neurology","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Endoc","valueLabel":"Endocrinology","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Oth","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"Neph","valueLabel":"Nephrology","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ortho","valueLabel":"Orthopaedic Surgery","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Surg","valueLabel":"Surgical","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Opth","valueLabel":"Opthalmology","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MxFx","valueLabel":"Maxillofacial Surgery","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Endoc","valueLabel":"Endocrinology","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Oth","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O195" t="str">
         <v>$SPECREV = 'Y'</v>
@@ -14138,7 +14138,7 @@
         <v>REVCLINTYP</v>
       </c>
       <c r="G202" t="str">
-        <v>If yes which clinic?</v>
+        <v>Review Clinic</v>
       </c>
       <c r="H202" t="str">
         <v>dropdown</v>
@@ -14159,7 +14159,7 @@
         <v>$REVCLIN = 'Y'</v>
       </c>
       <c r="N202" t="str">
-        <v>[{"value":"KMC","valueLabel":"Kangaroo clinic (Thursday)"},{"value":"NNC","valueLabel":"Neonatal clinic (Friday)"},{"value":"LOC","valueLabel":"Local clinic"},{"value":"SUR","valueLabel":"Surgical clinic"},{"value":"ORTH","valueLabel":"Orthopaedic clinic"},{"value":"OTH","valueLabel":"Other clinic"},{"value":"MFC","valueLabel":"Maxillofacial Clinic"},{"value":"PC","valueLabel":"Plastics Clinic"},{"value":"NSC","valueLabel":"Neuro Surgery Clinic"}]</v>
+        <v>[{"value":"KMC","valueLabel":"Kangaroo clinic (Thursday)"},{"value":"NNC","valueLabel":"Neonatal clinic (Friday)"},{"value":"LOC","valueLabel":"Local clinic"},{"value":"SUR","valueLabel":"Surgical clinic"},{"value":"ORTH","valueLabel":"Orthopaedic clinic"},{"value":"OTH","valueLabel":"Other clinic"},{"value":"MFC","valueLabel":"Maxillofacial Clinic"},{"value":"PC","valueLabel":"Plastics Clinic"}]</v>
       </c>
       <c r="O202" t="str">
         <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO'</v>
@@ -15090,7 +15090,7 @@
         <v>Gestation</v>
       </c>
       <c r="G216" t="str">
-        <v>Gestation (weeks.days)</v>
+        <v>Estimated Gestational age at birth (weeks.days)</v>
       </c>
       <c r="H216" t="str">
         <v>number</v>
@@ -16199,7 +16199,7 @@
         <v/>
       </c>
       <c r="N232" t="str">
-        <v>[{"value":"A","valueLabel":"African"},{"value":"AA","valueLabel":"African/AfricanAmerican"},{"value":"AS","valueLabel":"Asian/Pacific Islander"},{"value":"W","valueLabel":"White"},{"value":"NA","valueLabel":"NativeAmerican"},{"value":"O","valueLabel":"Other"}]</v>
+        <v>[{"value":"A","valueLabel":"African"},{"value":"AS","valueLabel":"Asian/Pacific Islander"},{"value":"W","valueLabel":"White"},{"value":"NA","valueLabel":"NativeAmerican"},{"value":"O","valueLabel":"Other"}]</v>
       </c>
       <c r="O232" t="str">
         <v>$NeoTreeOutcome = 'BID'</v>
@@ -16533,7 +16533,7 @@
         <v>Yes</v>
       </c>
       <c r="L237" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M237" t="str">
         <v/>
@@ -16719,10 +16719,10 @@
         <v>form</v>
       </c>
       <c r="F240" t="str">
-        <v>HAART</v>
+        <v>MaHAART</v>
       </c>
       <c r="G240" t="str">
-        <v>Mother on HAART?</v>
+        <v>Is the mother on HAART?</v>
       </c>
       <c r="H240" t="str">
         <v>dropdown</v>
@@ -16790,7 +16790,7 @@
         <v>LengthHAART</v>
       </c>
       <c r="G241" t="str">
-        <v>Mother on HAART since when?</v>
+        <v>Maternal HAART Initiation</v>
       </c>
       <c r="H241" t="str">
         <v>dropdown</v>
@@ -16808,7 +16808,7 @@
         <v>No</v>
       </c>
       <c r="M241" t="str">
-        <v>$HAART = 'Y'</v>
+        <v>$MaHAART = 'Y'</v>
       </c>
       <c r="N241" t="str">
         <v>[{"value":"1stTrim","valueLabel":"1st Trimester or earlier"},{"value":"2ndTrim","valueLabel":"2nd Trimester"},{"value":"3rdTrim","valueLabel":"3rd Trimester"}]</v>
@@ -18239,7 +18239,7 @@
         <v>$NeoTreeOutcome = 'BID'</v>
       </c>
       <c r="N262" t="str">
-        <v>[{"value":"PROM","valueLabel":"PROM more than 18 hrs","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MF","valueLabel":"Maternal fever in labour","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OL","valueLabel":"Offensive Liquor","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pr2nd","valueLabel":"Prolonged second stage","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival (BBA)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Prematurity &lt; 37 weeks","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
+        <v>[{"value":"PROM","valueLabel":"PROM more than 18 hrs","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MF","valueLabel":"Maternal fever in labour","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OL","valueLabel":"Offensive Liquor","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pr2nd","valueLabel":"Prolonged second stage labour","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival (BBA)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Prematurity &lt; 37 weeks","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O262" t="str">
         <v>$NeoTreeOutcome = 'BID'</v>
